--- a/zentao_description_audit_20260622.xlsx
+++ b/zentao_description_audit_20260622.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="71">
   <si>
     <t>Metric</t>
   </si>
@@ -36,13 +36,13 @@
     <t>Completion Rate</t>
   </si>
   <si>
-    <t>100.00%</t>
+    <t>75.00%</t>
   </si>
   <si>
     <t>Missing Rate</t>
   </si>
   <si>
-    <t>0.00%</t>
+    <t>25.00%</t>
   </si>
   <si>
     <t>Ticket ID</t>
@@ -133,6 +133,99 @@
   </si>
   <si>
     <t>http://pm.solusi-ku.id/zentao/task-view-906.html</t>
+  </si>
+  <si>
+    <t>920</t>
+  </si>
+  <si>
+    <t>Scrum 12/01/2026</t>
+  </si>
+  <si>
+    <t>Remapping Risk Register on management tools</t>
+  </si>
+  <si>
+    <t>On Progress</t>
+  </si>
+  <si>
+    <t>Missing Description</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-920.html</t>
+  </si>
+  <si>
+    <t>922</t>
+  </si>
+  <si>
+    <t>Create Report Assesment Core Banking System</t>
+  </si>
+  <si>
+    <t>Resolved</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-922.html</t>
+  </si>
+  <si>
+    <t>917</t>
+  </si>
+  <si>
+    <t>Implement CQRS for Funding History Monitoringx</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-917.html</t>
+  </si>
+  <si>
+    <t>916</t>
+  </si>
+  <si>
+    <t>Funding History Monitoring Integration on Lender Dashboard</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-916.html</t>
+  </si>
+  <si>
+    <t>914</t>
+  </si>
+  <si>
+    <t>UI for Activation of Existing RDL investors on Backoffice</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-914.html</t>
+  </si>
+  <si>
+    <t>913</t>
+  </si>
+  <si>
+    <t>API for Activation of Existing RDL investors on Backoffice</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-913.html</t>
+  </si>
+  <si>
+    <t>919</t>
+  </si>
+  <si>
+    <t>Implement Jira for management tools</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-919.html</t>
+  </si>
+  <si>
+    <t>918</t>
+  </si>
+  <si>
+    <t>Create action plan for ISO/IEC 27001:2022 audit findings</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-918.html</t>
+  </si>
+  <si>
+    <t>915</t>
+  </si>
+  <si>
+    <t>Create a Funding History Monitoring API on the Lender Dashboard</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-915.html</t>
   </si>
 </sst>
 </file>
@@ -166,7 +259,7 @@
       <color rgb="FFFF0000"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -186,6 +279,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF0F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -231,7 +329,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -257,8 +355,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -627,7 +730,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -635,7 +738,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -643,7 +746,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -670,7 +773,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -841,6 +944,186 @@
         <v>39</v>
       </c>
     </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -849,7 +1132,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -859,21 +1142,89 @@
     <col min="5" max="5" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:5" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="12" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/zentao_description_audit_20260622.xlsx
+++ b/zentao_description_audit_20260622.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2072" uniqueCount="638">
   <si>
     <t>Metric</t>
   </si>
@@ -36,13 +36,13 @@
     <t>Completion Rate</t>
   </si>
   <si>
-    <t>75.00%</t>
+    <t>25.59%</t>
   </si>
   <si>
     <t>Missing Rate</t>
   </si>
   <si>
-    <t>25.00%</t>
+    <t>74.41%</t>
   </si>
   <si>
     <t>Ticket ID</t>
@@ -226,6 +226,1707 @@
   </si>
   <si>
     <t>http://pm.solusi-ku.id/zentao/task-view-915.html</t>
+  </si>
+  <si>
+    <t>933</t>
+  </si>
+  <si>
+    <t>Scrum 19/01/2026</t>
+  </si>
+  <si>
+    <t>Add API to Receive Payment Notification</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-933.html</t>
+  </si>
+  <si>
+    <t>932</t>
+  </si>
+  <si>
+    <t>Get the status of a payment request</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-932.html</t>
+  </si>
+  <si>
+    <t>931</t>
+  </si>
+  <si>
+    <t>Add API to Create a payment request</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-931.html</t>
+  </si>
+  <si>
+    <t>930</t>
+  </si>
+  <si>
+    <t>Integration to Create a payment request</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-930.html</t>
+  </si>
+  <si>
+    <t>929</t>
+  </si>
+  <si>
+    <t>Add API to Receive Payment token notification</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-929.html</t>
+  </si>
+  <si>
+    <t>928</t>
+  </si>
+  <si>
+    <t>Add API to Check Status payment token</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-928.html</t>
+  </si>
+  <si>
+    <t>927</t>
+  </si>
+  <si>
+    <t>Add API to Create a new payment token</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-927.html</t>
+  </si>
+  <si>
+    <t>926</t>
+  </si>
+  <si>
+    <t>Update API Virtual Account Creation ("/loan/paymentCode")</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-926.html</t>
+  </si>
+  <si>
+    <t>925</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-925.html</t>
+  </si>
+  <si>
+    <t>924</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-924.html</t>
+  </si>
+  <si>
+    <t>923</t>
+  </si>
+  <si>
+    <t>Remapping risk register on Jira</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-923.html</t>
+  </si>
+  <si>
+    <t>945</t>
+  </si>
+  <si>
+    <t>Scrum 26/01/2026</t>
+  </si>
+  <si>
+    <t>Assist with Overall SOP Review for Non-IT Sections</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-945.html</t>
+  </si>
+  <si>
+    <t>944</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-944.html</t>
+  </si>
+  <si>
+    <t>943</t>
+  </si>
+  <si>
+    <t>Create API to Receive Payout Callback</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-943.html</t>
+  </si>
+  <si>
+    <t>942</t>
+  </si>
+  <si>
+    <t>Create API to Get all payouts by reference id</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-942.html</t>
+  </si>
+  <si>
+    <t>941</t>
+  </si>
+  <si>
+    <t>Create a Payout (Request deduction)</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-941.html</t>
+  </si>
+  <si>
+    <t>940</t>
+  </si>
+  <si>
+    <t>Update payment settlement order status</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-940.html</t>
+  </si>
+  <si>
+    <t>939</t>
+  </si>
+  <si>
+    <t>Schedule task to query payment links</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-939.html</t>
+  </si>
+  <si>
+    <t>938</t>
+  </si>
+  <si>
+    <t>Update notify repayment result</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-938.html</t>
+  </si>
+  <si>
+    <t>937</t>
+  </si>
+  <si>
+    <t>Update query repayment plan</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-937.html</t>
+  </si>
+  <si>
+    <t>936</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-936.html</t>
+  </si>
+  <si>
+    <t>935</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-935.html</t>
+  </si>
+  <si>
+    <t>934</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-934.html</t>
+  </si>
+  <si>
+    <t>955</t>
+  </si>
+  <si>
+    <t>Scrum 02/02/2026</t>
+  </si>
+  <si>
+    <t>Fulfill Self Assesment OJK</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-955.html</t>
+  </si>
+  <si>
+    <t>954</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-954.html</t>
+  </si>
+  <si>
+    <t>953</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-953.html</t>
+  </si>
+  <si>
+    <t>952</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-952.html</t>
+  </si>
+  <si>
+    <t>951</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-951.html</t>
+  </si>
+  <si>
+    <t>950</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-950.html</t>
+  </si>
+  <si>
+    <t>949</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-949.html</t>
+  </si>
+  <si>
+    <t>948</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-948.html</t>
+  </si>
+  <si>
+    <t>947</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-947.html</t>
+  </si>
+  <si>
+    <t>946</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-946.html</t>
+  </si>
+  <si>
+    <t>963</t>
+  </si>
+  <si>
+    <t>Scrum 09/02/2026</t>
+  </si>
+  <si>
+    <t>Wait</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-963.html</t>
+  </si>
+  <si>
+    <t>962</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-962.html</t>
+  </si>
+  <si>
+    <t>961</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-961.html</t>
+  </si>
+  <si>
+    <t>959</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-959.html</t>
+  </si>
+  <si>
+    <t>958</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-958.html</t>
+  </si>
+  <si>
+    <t>957</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-957.html</t>
+  </si>
+  <si>
+    <t>965</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-965.html</t>
+  </si>
+  <si>
+    <t>964</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-964.html</t>
+  </si>
+  <si>
+    <t>960</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-960.html</t>
+  </si>
+  <si>
+    <t>956</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-956.html</t>
+  </si>
+  <si>
+    <t>969</t>
+  </si>
+  <si>
+    <t>Scrum 16/02/2026</t>
+  </si>
+  <si>
+    <t>Data Filter on global configuration is not working</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-969.html</t>
+  </si>
+  <si>
+    <t>968</t>
+  </si>
+  <si>
+    <t>Adjust the filter because it is piling up</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-968.html</t>
+  </si>
+  <si>
+    <t>979</t>
+  </si>
+  <si>
+    <t>Scrum 23/02/2026</t>
+  </si>
+  <si>
+    <t>Add toolbar button to download withdrawal data</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-979.html</t>
+  </si>
+  <si>
+    <t>978</t>
+  </si>
+  <si>
+    <t>Create API to download withdrawal</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-978.html</t>
+  </si>
+  <si>
+    <t>977</t>
+  </si>
+  <si>
+    <t>Imrprovement SOP</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-977.html</t>
+  </si>
+  <si>
+    <t>976</t>
+  </si>
+  <si>
+    <t>Web Filtering configuration scheme</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-976.html</t>
+  </si>
+  <si>
+    <t>975</t>
+  </si>
+  <si>
+    <t>Secure code SOP update</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-975.html</t>
+  </si>
+  <si>
+    <t>974</t>
+  </si>
+  <si>
+    <t>Review of cloud-related configuration management SOP</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-974.html</t>
+  </si>
+  <si>
+    <t>973</t>
+  </si>
+  <si>
+    <t>Configuration management SOP review</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-973.html</t>
+  </si>
+  <si>
+    <t>972</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-972.html</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-971.html</t>
+  </si>
+  <si>
+    <t>970</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-970.html</t>
+  </si>
+  <si>
+    <t>987</t>
+  </si>
+  <si>
+    <t>Scrum 02/03/2026</t>
+  </si>
+  <si>
+    <t>Renew SOP ISO 27001:2022</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-987.html</t>
+  </si>
+  <si>
+    <t>986</t>
+  </si>
+  <si>
+    <t>Fullfil Internal Audit Finding</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-986.html</t>
+  </si>
+  <si>
+    <t>985</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-985.html</t>
+  </si>
+  <si>
+    <t>984</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-984.html</t>
+  </si>
+  <si>
+    <t>983</t>
+  </si>
+  <si>
+    <t>Improvement / SOP DLP</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-983.html</t>
+  </si>
+  <si>
+    <t>982</t>
+  </si>
+  <si>
+    <t>Improvement / SOP Threat Intellijen</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-982.html</t>
+  </si>
+  <si>
+    <t>981</t>
+  </si>
+  <si>
+    <t>Improvement / SOP Data Masking</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-981.html</t>
+  </si>
+  <si>
+    <t>980</t>
+  </si>
+  <si>
+    <t>Improvement / SOP BCP DRP</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-980.html</t>
+  </si>
+  <si>
+    <t>992</t>
+  </si>
+  <si>
+    <t>Scrum 09/03/2026</t>
+  </si>
+  <si>
+    <t>Implement UI for Downloading Funding History</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-992.html</t>
+  </si>
+  <si>
+    <t>991</t>
+  </si>
+  <si>
+    <t>Implement UI for Downloading Funding Opportunities</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-991.html</t>
+  </si>
+  <si>
+    <t>990</t>
+  </si>
+  <si>
+    <t>Optimize API for Lender Dashboard Preview</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-990.html</t>
+  </si>
+  <si>
+    <t>989</t>
+  </si>
+  <si>
+    <t>Develop Lender API to Download Funding History</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-989.html</t>
+  </si>
+  <si>
+    <t>988</t>
+  </si>
+  <si>
+    <t>Develop Lender API to Download Funding Opportunities</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-988.html</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>Scrum 16/03/2026</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1000.html</t>
+  </si>
+  <si>
+    <t>999</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-999.html</t>
+  </si>
+  <si>
+    <t>998</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-998.html</t>
+  </si>
+  <si>
+    <t>997</t>
+  </si>
+  <si>
+    <t>Create API for Xendit Payment token webhook notification</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-997.html</t>
+  </si>
+  <si>
+    <t>996</t>
+  </si>
+  <si>
+    <t>Update Parameter Notify repayment result based on settlement amount</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-996.html</t>
+  </si>
+  <si>
+    <t>995</t>
+  </si>
+  <si>
+    <t>Create API for Xendit payment session status Webhook</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-995.html</t>
+  </si>
+  <si>
+    <t>994</t>
+  </si>
+  <si>
+    <t>Create API for Xendit Query payment session status</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-994.html</t>
+  </si>
+  <si>
+    <t>993</t>
+  </si>
+  <si>
+    <t>Create API for Xendit payment session creation</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-993.html</t>
+  </si>
+  <si>
+    <t>1008</t>
+  </si>
+  <si>
+    <t>Scrum 23/03/2026</t>
+  </si>
+  <si>
+    <t>Add API to Request deduction</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1008.html</t>
+  </si>
+  <si>
+    <t>1007</t>
+  </si>
+  <si>
+    <t>Daily schedule task to check the settlement report</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1007.html</t>
+  </si>
+  <si>
+    <t>1006</t>
+  </si>
+  <si>
+    <t>Update payment capture status to notify disbursement backend</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1006.html</t>
+  </si>
+  <si>
+    <t>1005</t>
+  </si>
+  <si>
+    <t>Add API 'notification capture status' to Notify Disbursement Backend</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1005.html</t>
+  </si>
+  <si>
+    <t>1004</t>
+  </si>
+  <si>
+    <t>Add API request capture</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1004.html</t>
+  </si>
+  <si>
+    <t>1003</t>
+  </si>
+  <si>
+    <t>Add API to query token status</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1003.html</t>
+  </si>
+  <si>
+    <t>1002</t>
+  </si>
+  <si>
+    <t>Add API 'notification token status' to Notify Disbursement Backend update the token detail</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1002.html</t>
+  </si>
+  <si>
+    <t>1001</t>
+  </si>
+  <si>
+    <t>Update payment sesion status to notify disbursement backend</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1001.html</t>
+  </si>
+  <si>
+    <t>1021</t>
+  </si>
+  <si>
+    <t>Scrum 30/03/2026</t>
+  </si>
+  <si>
+    <t>Update the backup SOP to include a test restore.</t>
+  </si>
+  <si>
+    <t>Canceled</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1021.html</t>
+  </si>
+  <si>
+    <t>1019</t>
+  </si>
+  <si>
+    <t>(906) Implement CQRS to table v_loan_user_lender_funding (slow performance reported by 王茂霖(Morning Wang)</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1019.html</t>
+  </si>
+  <si>
+    <t>1018</t>
+  </si>
+  <si>
+    <t>(907) Implement CQRS to table v_loan_user_lender_funding_summary (slow performance reported by 王茂霖(Morning Wang)</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1018.html</t>
+  </si>
+  <si>
+    <t>1017</t>
+  </si>
+  <si>
+    <t>(908) Implement CQRS to table v_loan_user_lender_income (slow performance reported by 王茂霖(Morning Wang)</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1017.html</t>
+  </si>
+  <si>
+    <t>1016</t>
+  </si>
+  <si>
+    <t>(909) Implement CQRS to table v_loan_user_lender_offering (slow performance reported by 王茂霖(Morning Wang)</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1016.html</t>
+  </si>
+  <si>
+    <t>1015</t>
+  </si>
+  <si>
+    <t>(910) Implement CQRS to table v_loan_user_lender_product_summary (slow performance reported by 王茂霖(Morning Wang)</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1015.html</t>
+  </si>
+  <si>
+    <t>1014</t>
+  </si>
+  <si>
+    <t>(917) Implement CQRS for Funding History Monitoring</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1014.html</t>
+  </si>
+  <si>
+    <t>1013</t>
+  </si>
+  <si>
+    <t>(913) API for Activation of Existing RDL investors on Backoffice</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1013.html</t>
+  </si>
+  <si>
+    <t>1012</t>
+  </si>
+  <si>
+    <t>(914) UI for Activation of Existing RDL investors on Backoffice</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1012.html</t>
+  </si>
+  <si>
+    <t>1011</t>
+  </si>
+  <si>
+    <t>(916) Funding History Monitoring Integration on Lender Dashboard</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1011.html</t>
+  </si>
+  <si>
+    <t>1010</t>
+  </si>
+  <si>
+    <t>(933) Add API to Receive Payment Notification</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1010.html</t>
+  </si>
+  <si>
+    <t>1009</t>
+  </si>
+  <si>
+    <t>(932) Get the status of a payment request</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1009.html</t>
+  </si>
+  <si>
+    <t>1033</t>
+  </si>
+  <si>
+    <t>Follow-up and Coordination of ISO/IEC 27001:2022 Audit Findings</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1033.html</t>
+  </si>
+  <si>
+    <t>1032</t>
+  </si>
+  <si>
+    <t>Preparation of Finding Form for ISO/IEC 27001:2022 Recertification Audit</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1032.html</t>
+  </si>
+  <si>
+    <t>1031</t>
+  </si>
+  <si>
+    <t>ISO/IEC 27001:2022 Recertification Audit Execution</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1031.html</t>
+  </si>
+  <si>
+    <t>1024</t>
+  </si>
+  <si>
+    <t>Update the backup restore results documentation template (log data).</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1024.html</t>
+  </si>
+  <si>
+    <t>1023</t>
+  </si>
+  <si>
+    <t>Run a test restore (initial test) in a separate environment.</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1023.html</t>
+  </si>
+  <si>
+    <t>1022</t>
+  </si>
+  <si>
+    <t>Run a test backup of the server snapshot.</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1022.html</t>
+  </si>
+  <si>
+    <t>1020</t>
+  </si>
+  <si>
+    <t>(911) Adjust Lender Dashboard API using cached data</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1020.html</t>
+  </si>
+  <si>
+    <t>1039</t>
+  </si>
+  <si>
+    <t>Scrum 06/04/2026</t>
+  </si>
+  <si>
+    <t>API Integration Testing for Xignature Digital Signature via Sign Gateway</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1039.html</t>
+  </si>
+  <si>
+    <t>1037</t>
+  </si>
+  <si>
+    <t>Process Analysis Report to Update Settlement order status</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1037.html</t>
+  </si>
+  <si>
+    <t>1036</t>
+  </si>
+  <si>
+    <t>Query the generate status of report</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1036.html</t>
+  </si>
+  <si>
+    <t>1035</t>
+  </si>
+  <si>
+    <t>Create Request to generate the settlement report</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1035.html</t>
+  </si>
+  <si>
+    <t>1034</t>
+  </si>
+  <si>
+    <t>Backoffice FE - Implement Email Field in User Form Modal</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1034.html</t>
+  </si>
+  <si>
+    <t>1030</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1030.html</t>
+  </si>
+  <si>
+    <t>1029</t>
+  </si>
+  <si>
+    <t>Run a test restore (initial test) in a separate environment</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1029.html</t>
+  </si>
+  <si>
+    <t>1028</t>
+  </si>
+  <si>
+    <t>Run a test backup of the server snapshot</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1028.html</t>
+  </si>
+  <si>
+    <t>1027</t>
+  </si>
+  <si>
+    <t>Display success message after withdrawal download completion</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1027.html</t>
+  </si>
+  <si>
+    <t>1026</t>
+  </si>
+  <si>
+    <t>Refactor backoffice withdrawal download from synchronous to asynchronous</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1026.html</t>
+  </si>
+  <si>
+    <t>1025</t>
+  </si>
+  <si>
+    <t>Conduct testing for Payment Capture (Phase 2)</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1025.html</t>
+  </si>
+  <si>
+    <t>1038</t>
+  </si>
+  <si>
+    <t>Create Request deduction</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1038.html</t>
+  </si>
+  <si>
+    <t>1058</t>
+  </si>
+  <si>
+    <t>Scrum 13/04/2026</t>
+  </si>
+  <si>
+    <t>Supporting Document protection against malware</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1058.html</t>
+  </si>
+  <si>
+    <t>1049</t>
+  </si>
+  <si>
+    <t>SOP BCP/DRP</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1049.html</t>
+  </si>
+  <si>
+    <t>1046</t>
+  </si>
+  <si>
+    <t>Fullfil Document for Audit Finance</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1046.html</t>
+  </si>
+  <si>
+    <t>1045</t>
+  </si>
+  <si>
+    <t>Preparation Audit Finance related IT</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1045.html</t>
+  </si>
+  <si>
+    <t>1047</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1047.html</t>
+  </si>
+  <si>
+    <t>1057</t>
+  </si>
+  <si>
+    <t>Supporting Document Capacity management</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1057.html</t>
+  </si>
+  <si>
+    <t>1048</t>
+  </si>
+  <si>
+    <t>SOP Risk Management</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1048.html</t>
+  </si>
+  <si>
+    <t>1044</t>
+  </si>
+  <si>
+    <t>Supporting Fullfil Audit Finance related IT Security</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1044.html</t>
+  </si>
+  <si>
+    <t>1043</t>
+  </si>
+  <si>
+    <t>Action Plan pre DRC preparation</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1043.html</t>
+  </si>
+  <si>
+    <t>1042</t>
+  </si>
+  <si>
+    <t>Create pre action Plan DRC</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1042.html</t>
+  </si>
+  <si>
+    <t>1041</t>
+  </si>
+  <si>
+    <t>Check borrower balance still remain in Instamoney</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1041.html</t>
+  </si>
+  <si>
+    <t>1040</t>
+  </si>
+  <si>
+    <t>Conduct testing for Payment Settlement (Phase 3)</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1040.html</t>
+  </si>
+  <si>
+    <t>1069</t>
+  </si>
+  <si>
+    <t>Scrum 20/04/2026</t>
+  </si>
+  <si>
+    <t>Supporting Revision Audit Finance ITGC 2026</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1069.html</t>
+  </si>
+  <si>
+    <t>1056</t>
+  </si>
+  <si>
+    <t>Renew SOP ISO 27001:2022 - Web filtering</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1056.html</t>
+  </si>
+  <si>
+    <t>1055</t>
+  </si>
+  <si>
+    <t>Renew SOP ISO 27001:2022 -  Information backup</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1055.html</t>
+  </si>
+  <si>
+    <t>1054</t>
+  </si>
+  <si>
+    <t>Renew SOP ISO 27001:2022 - Information Security Policy</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1054.html</t>
+  </si>
+  <si>
+    <t>1053</t>
+  </si>
+  <si>
+    <t>Investigation &amp; Performance Tuning: /loan/application/requestLoan</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1053.html</t>
+  </si>
+  <si>
+    <t>1052</t>
+  </si>
+  <si>
+    <t>Create new 50 Lender's VA for TECH LUCK INDONESIA</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1052.html</t>
+  </si>
+  <si>
+    <t>1051</t>
+  </si>
+  <si>
+    <t>Add failed withdrawal retry procedure</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1051.html</t>
+  </si>
+  <si>
+    <t>1050</t>
+  </si>
+  <si>
+    <t>Send alert on failed daily withdrawal</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1050.html</t>
+  </si>
+  <si>
+    <t>1068</t>
+  </si>
+  <si>
+    <t>Scrum27/04/2026</t>
+  </si>
+  <si>
+    <t>Preparation of New SOPs based on Gap Audit</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1068.html</t>
+  </si>
+  <si>
+    <t>1067</t>
+  </si>
+  <si>
+    <t>Review and Update SOP IT according to ISO 27001</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1067.html</t>
+  </si>
+  <si>
+    <t>1077</t>
+  </si>
+  <si>
+    <t>Internal transfer for stuck disbursements.</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1077.html</t>
+  </si>
+  <si>
+    <t>1076</t>
+  </si>
+  <si>
+    <t>Created Business Impact Analysis Document</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1076.html</t>
+  </si>
+  <si>
+    <t>1075</t>
+  </si>
+  <si>
+    <t>Created Test Plan Disaster Recovery Plan (DRP)</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1075.html</t>
+  </si>
+  <si>
+    <t>1074</t>
+  </si>
+  <si>
+    <t>Created Recovery Strategy Analysis Document</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1074.html</t>
+  </si>
+  <si>
+    <t>1073</t>
+  </si>
+  <si>
+    <t>Implement Retry Mechanism for Internal Transfers</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1073.html</t>
+  </si>
+  <si>
+    <t>1072</t>
+  </si>
+  <si>
+    <t>Optimization General Performance Improvements and Minor Refactoring on read report CSV</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1072.html</t>
+  </si>
+  <si>
+    <t>1071</t>
+  </si>
+  <si>
+    <t>Drafting a management response document on the results of the ITGC review</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1071.html</t>
+  </si>
+  <si>
+    <t>1070</t>
+  </si>
+  <si>
+    <t>Summarize temporary finding ITGC audit finance</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1070.html</t>
+  </si>
+  <si>
+    <t>1066</t>
+  </si>
+  <si>
+    <t>Implementation of Audit Finding Improvements</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1066.html</t>
+  </si>
+  <si>
+    <t>1065</t>
+  </si>
+  <si>
+    <t>Preparation of Corrective Action Plan for Audit Results</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1065.html</t>
+  </si>
+  <si>
+    <t>1064</t>
+  </si>
+  <si>
+    <t>[UI] Add Cashflow Export Functionality to Backoffice Toolbar</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1064.html</t>
+  </si>
+  <si>
+    <t>1063</t>
+  </si>
+  <si>
+    <t>[UI] Implement Payment Data Export Button in Backoffice Toolbar</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1063.html</t>
+  </si>
+  <si>
+    <t>1062</t>
+  </si>
+  <si>
+    <t>[UI] Add Export Button for Loan Order Data in Backoffice Toolbar</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1062.html</t>
+  </si>
+  <si>
+    <t>1061</t>
+  </si>
+  <si>
+    <t>[API] Create Backoffice API for Cashflow Data Export</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1061.html</t>
+  </si>
+  <si>
+    <t>1060</t>
+  </si>
+  <si>
+    <t>[API] Develop Backoffice API for Payment Data Export</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1060.html</t>
+  </si>
+  <si>
+    <t>1059</t>
+  </si>
+  <si>
+    <t>[API] Implement Backoffice API for Loan Order Data Export</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1059.html</t>
+  </si>
+  <si>
+    <t>1081</t>
+  </si>
+  <si>
+    <t>Scrum 04/05/2026</t>
+  </si>
+  <si>
+    <t>Replace event type from: payment_session.completed to payment.capture</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1081.html</t>
+  </si>
+  <si>
+    <t>1080</t>
+  </si>
+  <si>
+    <t>Setup Payment Monitoring Schedule: Instamoney VA</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1080.html</t>
+  </si>
+  <si>
+    <t>1079</t>
+  </si>
+  <si>
+    <t>Setup Payment Monitoring Schedule: Alfamart</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1079.html</t>
+  </si>
+  <si>
+    <t>1078</t>
+  </si>
+  <si>
+    <t>Setup Payment Monitoring Schedule: Xendit</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1078.html</t>
+  </si>
+  <si>
+    <t>1087</t>
+  </si>
+  <si>
+    <t>Scrum 11/05/2026</t>
+  </si>
+  <si>
+    <t>Identify New IT Risks</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1087.html</t>
+  </si>
+  <si>
+    <t>1086</t>
+  </si>
+  <si>
+    <t>IT Residual Risk Review and Evaluation</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1086.html</t>
+  </si>
+  <si>
+    <t>1085</t>
+  </si>
+  <si>
+    <t>Review Implementation Server Hardening</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1085.html</t>
+  </si>
+  <si>
+    <t>1083</t>
+  </si>
+  <si>
+    <t>Monitoring Corrective Action Plan (CAPA) and Audit Finding Status</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1083.html</t>
+  </si>
+  <si>
+    <t>1084</t>
+  </si>
+  <si>
+    <t>Backup &amp; Restore Evidence Review and Validation</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1084.html</t>
+  </si>
+  <si>
+    <t>1082</t>
+  </si>
+  <si>
+    <t>Technical Guide for Server Operations</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1082.html</t>
+  </si>
+  <si>
+    <t>1090</t>
+  </si>
+  <si>
+    <t>Scrum 18/05/2026</t>
+  </si>
+  <si>
+    <t>Network Connectivity: WireGuard VPN Tunnel Setup</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1090.html</t>
+  </si>
+  <si>
+    <t>1089</t>
+  </si>
+  <si>
+    <t>Disable Destination Virtual Account Number &amp; Verify Notice to Disbursement Backend (Ref ID: 1778934540308594272)</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1089.html</t>
+  </si>
+  <si>
+    <t>1088</t>
+  </si>
+  <si>
+    <t>Implement Retry Mechanism for RDL Transfer Request</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1088.html</t>
+  </si>
+  <si>
+    <t>1092</t>
+  </si>
+  <si>
+    <t>Scrum 25/05/2026</t>
+  </si>
+  <si>
+    <t>Remove "HAPUS BUKU (WO)" and "RESTRUKTURISASI" Buttons from Riwayat Pendanaan Page</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1092.html</t>
+  </si>
+  <si>
+    <t>1091</t>
+  </si>
+  <si>
+    <t>[Backoffice] UI/UX Refactoring and Popup Edit Functionality on Global Configuration Page</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1091.html</t>
+  </si>
+  <si>
+    <t>1097</t>
+  </si>
+  <si>
+    <t>Scrum 01/06/2026</t>
+  </si>
+  <si>
+    <t>UI to display "Log Activity" for Lender</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1097.html</t>
+  </si>
+  <si>
+    <t>1096</t>
+  </si>
+  <si>
+    <t>Create API for Lender "Log Activity"</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1096.html</t>
+  </si>
+  <si>
+    <t>1095</t>
+  </si>
+  <si>
+    <t>Implement Audit trail Log for Platform</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1095.html</t>
+  </si>
+  <si>
+    <t>1094</t>
+  </si>
+  <si>
+    <t>Implement Audit trail Log for Lender</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1094.html</t>
+  </si>
+  <si>
+    <t>1093</t>
+  </si>
+  <si>
+    <t>Implement Retry Mechanism for Repayment</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1093.html</t>
+  </si>
+  <si>
+    <t>1116</t>
+  </si>
+  <si>
+    <t>Scrum 15/06/2026</t>
+  </si>
+  <si>
+    <t>Implement Tito &amp; PEMBERI PINJAMAN Stamp Placement on Generated Restructuring Agreement PDF</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1116.html</t>
+  </si>
+  <si>
+    <t>1112</t>
+  </si>
+  <si>
+    <t>Loan Transaction export</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1112.html</t>
+  </si>
+  <si>
+    <t>1111</t>
+  </si>
+  <si>
+    <t>Withdrawal export</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1111.html</t>
+  </si>
+  <si>
+    <t>1110</t>
+  </si>
+  <si>
+    <t>Disbursement export</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1110.html</t>
+  </si>
+  <si>
+    <t>1109</t>
+  </si>
+  <si>
+    <t>Migrate cashflow/payment/loan-order to the template + fix the cross-DTO bug</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1109.html</t>
+  </si>
+  <si>
+    <t>1108</t>
+  </si>
+  <si>
+    <t>Refactor async export into a generic pattern (ExcelWriter + AsyncExportTemplate)</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1108.html</t>
+  </si>
+  <si>
+    <t>1105</t>
+  </si>
+  <si>
+    <t>Register Instances as wg peers</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1105.html</t>
+  </si>
+  <si>
+    <t>1104</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1104.html</t>
+  </si>
+  <si>
+    <t>1099</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1099.html</t>
+  </si>
+  <si>
+    <t>1098</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1098.html</t>
+  </si>
+  <si>
+    <t>1119</t>
+  </si>
+  <si>
+    <t>Scrum 22/06/2026</t>
+  </si>
+  <si>
+    <t>Loan Transaction Page</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1119.html</t>
+  </si>
+  <si>
+    <t>1118</t>
+  </si>
+  <si>
+    <t>Withdrawal Page</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1118.html</t>
+  </si>
+  <si>
+    <t>1117</t>
+  </si>
+  <si>
+    <t>Disbursement Page</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1117.html</t>
+  </si>
+  <si>
+    <t>1115</t>
+  </si>
+  <si>
+    <t>Establish Secure Connectivity Between Alibaba ECS and On-Premise Wazuh SIEM</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1115.html</t>
+  </si>
+  <si>
+    <t>1114</t>
+  </si>
+  <si>
+    <t>Export button on Disbursement, Withdrawal, Transaction pages</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1114.html</t>
+  </si>
+  <si>
+    <t>1113</t>
+  </si>
+  <si>
+    <t>Contract / Contract Cashflow / Contact export</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1113.html</t>
+  </si>
+  <si>
+    <t>1107</t>
+  </si>
+  <si>
+    <t>Create the Runbook and Recovery Procedure</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1107.html</t>
+  </si>
+  <si>
+    <t>1106</t>
+  </si>
+  <si>
+    <t>Validate SIEM Wazuh Agent Connectivity</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1106.html</t>
+  </si>
+  <si>
+    <t>1103</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1103.html</t>
+  </si>
+  <si>
+    <t>1102</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1102.html</t>
+  </si>
+  <si>
+    <t>1101</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1101.html</t>
+  </si>
+  <si>
+    <t>1100</t>
+  </si>
+  <si>
+    <t>http://pm.solusi-ku.id/zentao/task-view-1100.html</t>
   </si>
 </sst>
 </file>
@@ -730,7 +2431,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3">
-        <v>16</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -738,7 +2439,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3">
-        <v>12</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -746,7 +2447,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="3">
-        <v>4</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -773,7 +2474,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F212"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1124,6 +2825,3906 @@
         <v>70</v>
       </c>
     </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E46" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E47" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E48" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E49" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E50" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E51" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E52" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E53" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E54" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E55" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E56" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E57" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E58" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="D59" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E59" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E60" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="D61" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E61" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E62" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="D63" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E63" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E64" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="D65" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E65" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E66" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="D67" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E67" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E68" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="D69" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E69" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E70" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F70" s="6" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="D71" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E71" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E72" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="B73" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="C73" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="D73" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E73" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E74" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="B75" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D75" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E75" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F75" s="9" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E76" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F76" s="6" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="D77" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E77" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F77" s="9" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E78" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="C79" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="D79" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E79" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F79" s="9" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E80" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F80" s="6" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="C81" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="D81" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E81" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F81" s="9" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E82" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F82" s="6" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="B83" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="C83" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="D83" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E83" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F83" s="9" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E84" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F84" s="6" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="B85" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="C85" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="D85" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E85" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F85" s="9" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E86" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F86" s="6" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="B87" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="C87" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="D87" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E87" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F87" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E88" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F88" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="B89" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="C89" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="D89" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E89" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F89" s="9" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E90" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F90" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="B91" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="C91" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="D91" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E91" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F91" s="9" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E92" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F92" s="6" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="B93" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="C93" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="D93" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E93" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F93" s="9" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E94" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="B95" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="C95" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="D95" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E95" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F95" s="9" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="D96" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E96" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F96" s="6" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="B97" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="C97" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="D97" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E97" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F97" s="9" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E98" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F98" s="6" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="B99" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="C99" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="D99" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E99" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F99" s="9" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E100" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F100" s="6" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="B101" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="C101" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="D101" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E101" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F101" s="9" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B102" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="E102" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F102" s="6" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="B103" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="C103" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="D103" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="E103" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F103" s="9" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="E104" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F104" s="6" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="B105" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="C105" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="D105" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="E105" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F105" s="9" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="E106" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F106" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="B107" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="C107" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="D107" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="E107" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F107" s="9" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="D108" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="E108" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F108" s="6" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="B109" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="C109" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="D109" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="E109" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F109" s="9" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="B110" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="D110" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="E110" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F110" s="6" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="B111" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="C111" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="D111" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="E111" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F111" s="9" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="B112" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="D112" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="E112" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F112" s="6" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="B113" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="C113" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="D113" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="E113" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F113" s="9" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="D114" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E114" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F114" s="6" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="B115" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="C115" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="D115" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E115" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F115" s="9" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="D116" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E116" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F116" s="6" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="B117" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="C117" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="D117" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E117" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F117" s="9" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="B118" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="D118" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E118" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F118" s="6" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="B119" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="C119" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="D119" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E119" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F119" s="9" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="B120" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="D120" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E120" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F120" s="6" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="B121" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="C121" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="D121" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E121" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F121" s="9" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="B122" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="D122" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E122" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F122" s="6" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="B123" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="C123" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="D123" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E123" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F123" s="9" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="B124" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="D124" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E124" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F124" s="6" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="B125" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="C125" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="D125" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E125" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F125" s="9" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="B126" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="D126" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E126" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F126" s="6" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="B127" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="C127" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="D127" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E127" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F127" s="9" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="B128" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="D128" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E128" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F128" s="6" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="B129" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="C129" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="D129" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E129" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F129" s="9" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="B130" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="D130" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E130" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F130" s="6" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="B131" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="C131" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="D131" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E131" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F131" s="9" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="B132" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="D132" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E132" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F132" s="6" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="B133" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="C133" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="D133" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E133" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F133" s="9" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="B134" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="D134" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E134" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F134" s="6" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="B135" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="C135" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="D135" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E135" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F135" s="9" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="B136" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="D136" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E136" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F136" s="6" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="B137" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="C137" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="D137" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E137" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F137" s="9" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="B138" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="C138" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="D138" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E138" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F138" s="6" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="B139" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="C139" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="D139" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E139" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F139" s="9" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="B140" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="C140" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="D140" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E140" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F140" s="6" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="B141" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="C141" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="D141" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E141" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F141" s="9" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="B142" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="C142" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="D142" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E142" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F142" s="6" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="B143" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="C143" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="D143" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E143" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F143" s="9" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="B144" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="C144" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="D144" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E144" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F144" s="6" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="B145" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="C145" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="D145" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E145" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F145" s="9" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A146" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="C146" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="D146" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E146" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F146" s="6" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="B147" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="C147" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="D147" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E147" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F147" s="9" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A148" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="B148" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="C148" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="D148" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E148" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F148" s="6" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A149" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="B149" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="C149" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="D149" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E149" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F149" s="9" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A150" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="B150" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="C150" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="D150" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E150" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F150" s="6" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A151" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="B151" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="C151" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="D151" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E151" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F151" s="9" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="C152" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="D152" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E152" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F152" s="6" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A153" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="B153" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="C153" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="D153" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E153" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F153" s="9" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A154" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="B154" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="C154" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="D154" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E154" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F154" s="6" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A155" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="B155" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="C155" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="D155" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E155" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F155" s="9" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A156" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="D156" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E156" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F156" s="6" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A157" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="B157" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="C157" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="D157" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E157" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F157" s="9" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A158" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="B158" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="C158" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="D158" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E158" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F158" s="6" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A159" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="B159" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="C159" s="9" t="s">
+        <v>477</v>
+      </c>
+      <c r="D159" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E159" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F159" s="9" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A160" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="B160" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="D160" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E160" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F160" s="6" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A161" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="B161" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="C161" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="D161" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E161" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F161" s="9" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A162" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="B162" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="C162" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="D162" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E162" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F162" s="6" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A163" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="B163" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="C163" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="D163" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E163" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F163" s="9" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A164" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="B164" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="C164" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="D164" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E164" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F164" s="6" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A165" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="B165" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="C165" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="D165" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E165" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F165" s="9" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A166" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="B166" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="C166" s="6" t="s">
+        <v>498</v>
+      </c>
+      <c r="D166" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E166" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F166" s="6" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A167" s="9" t="s">
+        <v>500</v>
+      </c>
+      <c r="B167" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="C167" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="D167" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E167" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F167" s="9" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A168" s="6" t="s">
+        <v>503</v>
+      </c>
+      <c r="B168" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="C168" s="6" t="s">
+        <v>504</v>
+      </c>
+      <c r="D168" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E168" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F168" s="6" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A169" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="B169" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="C169" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="D169" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E169" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F169" s="9" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A170" s="6" t="s">
+        <v>509</v>
+      </c>
+      <c r="B170" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="C170" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="D170" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E170" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F170" s="6" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A171" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="B171" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="C171" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="D171" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E171" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F171" s="9" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A172" s="6" t="s">
+        <v>516</v>
+      </c>
+      <c r="B172" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="D172" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E172" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F172" s="6" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A173" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="B173" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="C173" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="D173" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E173" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F173" s="9" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A174" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="B174" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="C174" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="D174" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E174" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F174" s="6" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A175" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="B175" s="9" t="s">
+        <v>526</v>
+      </c>
+      <c r="C175" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="D175" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E175" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F175" s="9" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A176" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="B176" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="C176" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="D176" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E176" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F176" s="6" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A177" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="B177" s="9" t="s">
+        <v>526</v>
+      </c>
+      <c r="C177" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="D177" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E177" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F177" s="9" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A178" s="6" t="s">
+        <v>535</v>
+      </c>
+      <c r="B178" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="C178" s="6" t="s">
+        <v>536</v>
+      </c>
+      <c r="D178" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E178" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F178" s="6" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A179" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="B179" s="9" t="s">
+        <v>526</v>
+      </c>
+      <c r="C179" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="D179" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E179" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F179" s="9" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A180" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="B180" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="C180" s="6" t="s">
+        <v>542</v>
+      </c>
+      <c r="D180" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E180" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F180" s="6" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A181" s="9" t="s">
+        <v>544</v>
+      </c>
+      <c r="B181" s="9" t="s">
+        <v>545</v>
+      </c>
+      <c r="C181" s="9" t="s">
+        <v>546</v>
+      </c>
+      <c r="D181" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E181" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F181" s="9" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A182" s="6" t="s">
+        <v>548</v>
+      </c>
+      <c r="B182" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="C182" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="D182" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E182" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F182" s="6" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A183" s="9" t="s">
+        <v>551</v>
+      </c>
+      <c r="B183" s="9" t="s">
+        <v>545</v>
+      </c>
+      <c r="C183" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="D183" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E183" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F183" s="9" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A184" s="6" t="s">
+        <v>554</v>
+      </c>
+      <c r="B184" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="C184" s="6" t="s">
+        <v>556</v>
+      </c>
+      <c r="D184" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E184" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F184" s="6" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A185" s="9" t="s">
+        <v>558</v>
+      </c>
+      <c r="B185" s="9" t="s">
+        <v>555</v>
+      </c>
+      <c r="C185" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="D185" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E185" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F185" s="9" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A186" s="6" t="s">
+        <v>561</v>
+      </c>
+      <c r="B186" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="C186" s="6" t="s">
+        <v>563</v>
+      </c>
+      <c r="D186" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E186" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F186" s="6" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A187" s="9" t="s">
+        <v>565</v>
+      </c>
+      <c r="B187" s="9" t="s">
+        <v>562</v>
+      </c>
+      <c r="C187" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="D187" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E187" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F187" s="9" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A188" s="6" t="s">
+        <v>568</v>
+      </c>
+      <c r="B188" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="C188" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="D188" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E188" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F188" s="6" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A189" s="9" t="s">
+        <v>571</v>
+      </c>
+      <c r="B189" s="9" t="s">
+        <v>562</v>
+      </c>
+      <c r="C189" s="9" t="s">
+        <v>572</v>
+      </c>
+      <c r="D189" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E189" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F189" s="9" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A190" s="6" t="s">
+        <v>574</v>
+      </c>
+      <c r="B190" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="C190" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="D190" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E190" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F190" s="6" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A191" s="9" t="s">
+        <v>577</v>
+      </c>
+      <c r="B191" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="C191" s="9" t="s">
+        <v>579</v>
+      </c>
+      <c r="D191" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E191" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F191" s="9" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A192" s="6" t="s">
+        <v>581</v>
+      </c>
+      <c r="B192" s="6" t="s">
+        <v>578</v>
+      </c>
+      <c r="C192" s="6" t="s">
+        <v>582</v>
+      </c>
+      <c r="D192" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E192" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F192" s="6" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A193" s="9" t="s">
+        <v>584</v>
+      </c>
+      <c r="B193" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="C193" s="9" t="s">
+        <v>585</v>
+      </c>
+      <c r="D193" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E193" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F193" s="9" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A194" s="6" t="s">
+        <v>587</v>
+      </c>
+      <c r="B194" s="6" t="s">
+        <v>578</v>
+      </c>
+      <c r="C194" s="6" t="s">
+        <v>588</v>
+      </c>
+      <c r="D194" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E194" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F194" s="6" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A195" s="9" t="s">
+        <v>590</v>
+      </c>
+      <c r="B195" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="C195" s="9" t="s">
+        <v>591</v>
+      </c>
+      <c r="D195" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E195" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F195" s="9" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A196" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="B196" s="6" t="s">
+        <v>578</v>
+      </c>
+      <c r="C196" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="D196" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E196" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F196" s="6" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A197" s="9" t="s">
+        <v>596</v>
+      </c>
+      <c r="B197" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="C197" s="9" t="s">
+        <v>597</v>
+      </c>
+      <c r="D197" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E197" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F197" s="9" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A198" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="B198" s="6" t="s">
+        <v>578</v>
+      </c>
+      <c r="C198" s="6" t="s">
+        <v>546</v>
+      </c>
+      <c r="D198" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E198" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F198" s="6" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A199" s="9" t="s">
+        <v>601</v>
+      </c>
+      <c r="B199" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="C199" s="9" t="s">
+        <v>569</v>
+      </c>
+      <c r="D199" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E199" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F199" s="9" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A200" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="B200" s="6" t="s">
+        <v>578</v>
+      </c>
+      <c r="C200" s="6" t="s">
+        <v>563</v>
+      </c>
+      <c r="D200" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E200" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F200" s="6" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A201" s="9" t="s">
+        <v>605</v>
+      </c>
+      <c r="B201" s="9" t="s">
+        <v>606</v>
+      </c>
+      <c r="C201" s="9" t="s">
+        <v>607</v>
+      </c>
+      <c r="D201" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E201" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F201" s="9" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A202" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="B202" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="C202" s="6" t="s">
+        <v>610</v>
+      </c>
+      <c r="D202" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E202" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F202" s="6" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A203" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="B203" s="9" t="s">
+        <v>606</v>
+      </c>
+      <c r="C203" s="9" t="s">
+        <v>613</v>
+      </c>
+      <c r="D203" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E203" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F203" s="9" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A204" s="6" t="s">
+        <v>615</v>
+      </c>
+      <c r="B204" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="C204" s="6" t="s">
+        <v>616</v>
+      </c>
+      <c r="D204" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E204" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F204" s="6" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A205" s="9" t="s">
+        <v>618</v>
+      </c>
+      <c r="B205" s="9" t="s">
+        <v>606</v>
+      </c>
+      <c r="C205" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D205" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E205" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F205" s="9" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A206" s="6" t="s">
+        <v>621</v>
+      </c>
+      <c r="B206" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="C206" s="6" t="s">
+        <v>622</v>
+      </c>
+      <c r="D206" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E206" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F206" s="6" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A207" s="9" t="s">
+        <v>624</v>
+      </c>
+      <c r="B207" s="9" t="s">
+        <v>606</v>
+      </c>
+      <c r="C207" s="9" t="s">
+        <v>625</v>
+      </c>
+      <c r="D207" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E207" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F207" s="9" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A208" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="B208" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="C208" s="6" t="s">
+        <v>628</v>
+      </c>
+      <c r="D208" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E208" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F208" s="6" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A209" s="9" t="s">
+        <v>630</v>
+      </c>
+      <c r="B209" s="9" t="s">
+        <v>606</v>
+      </c>
+      <c r="C209" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="D209" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E209" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F209" s="9" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A210" s="6" t="s">
+        <v>632</v>
+      </c>
+      <c r="B210" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="C210" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="D210" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E210" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F210" s="6" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A211" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="B211" s="9" t="s">
+        <v>606</v>
+      </c>
+      <c r="C211" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="D211" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E211" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F211" s="9" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A212" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="B212" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="C212" s="6" t="s">
+        <v>536</v>
+      </c>
+      <c r="D212" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E212" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F212" s="6" t="s">
+        <v>637</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1132,7 +6733,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E158"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1227,6 +6828,2607 @@
         <v>67</v>
       </c>
     </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="D38" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D40" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="E40" s="13" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="D42" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="E42" s="13" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D44" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="D46" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E46" s="13" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E47" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="B48" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="D48" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E48" s="13" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="D50" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E50" s="13" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E51" s="9" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="B52" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="C52" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="D52" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E52" s="13" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="D54" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E54" s="13" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="B56" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="C56" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="D56" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E56" s="13" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="B58" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D58" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E58" s="13" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="D59" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E59" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="B60" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="D60" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="E60" s="13" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D61" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="B62" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="C62" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="D62" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E62" s="13" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="D63" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E63" s="9" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="B64" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="C64" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="D64" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E64" s="13" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="D65" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E65" s="9" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="B66" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="C66" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="D66" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E66" s="13" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="D67" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E67" s="9" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="B68" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="C68" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="D68" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E68" s="13" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="D69" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E69" s="9" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="B70" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="C70" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="D70" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E70" s="13" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="D71" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E71" s="9" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="B72" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="C72" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="D72" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="E72" s="13" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="B73" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="C73" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="D73" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E73" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="B74" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="C74" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="D74" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="E74" s="13" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="B75" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="D75" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E75" s="9" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="B76" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="C76" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="D76" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E76" s="13" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="D77" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E77" s="9" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="B78" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="C78" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="D78" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E78" s="13" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="C79" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="D79" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E79" s="9" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="B80" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="C80" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="D80" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E80" s="13" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="C81" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="D81" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E81" s="9" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="B82" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="C82" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D82" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E82" s="13" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="B83" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="C83" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="D83" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E83" s="9" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="B84" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="C84" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="D84" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E84" s="13" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="B85" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="C85" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="D85" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E85" s="9" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="13" t="s">
+        <v>295</v>
+      </c>
+      <c r="B86" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="C86" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="D86" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E86" s="13" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="B87" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="C87" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="D87" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E87" s="9" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="B88" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="C88" s="13" t="s">
+        <v>303</v>
+      </c>
+      <c r="D88" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="E88" s="13" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="B89" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="C89" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="D89" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="E89" s="9" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="13" t="s">
+        <v>309</v>
+      </c>
+      <c r="B90" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="C90" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="D90" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="E90" s="13" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="B91" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="C91" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="D91" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="E91" s="9" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="B92" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="C92" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="D92" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="E92" s="13" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="B93" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="C93" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="D93" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="E93" s="9" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="B94" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="C94" s="13" t="s">
+        <v>322</v>
+      </c>
+      <c r="D94" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="E94" s="13" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="B95" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="C95" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="D95" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="E95" s="9" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="B96" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="C96" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="D96" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="E96" s="13" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="B97" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="C97" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="D97" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="E97" s="9" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="13" t="s">
+        <v>333</v>
+      </c>
+      <c r="B98" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="C98" s="13" t="s">
+        <v>334</v>
+      </c>
+      <c r="D98" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="E98" s="13" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="B99" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="C99" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="D99" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="E99" s="9" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="13" t="s">
+        <v>339</v>
+      </c>
+      <c r="B100" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="C100" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="D100" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E100" s="13" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="B101" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="C101" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="D101" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E101" s="9" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="B102" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="C102" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="D102" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E102" s="13" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="B103" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="C103" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="D103" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E103" s="9" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="13" t="s">
+        <v>351</v>
+      </c>
+      <c r="B104" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="C104" s="13" t="s">
+        <v>352</v>
+      </c>
+      <c r="D104" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E104" s="13" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="B105" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="C105" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="D105" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E105" s="9" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="B106" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="C106" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="D106" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E106" s="13" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="B107" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="C107" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="D107" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E107" s="9" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="B108" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="C108" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="D108" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E108" s="13" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="B109" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="C109" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="D109" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E109" s="9" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="13" t="s">
+        <v>378</v>
+      </c>
+      <c r="B110" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="C110" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="D110" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E110" s="13" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="B111" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="C111" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="D111" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E111" s="9" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="13" t="s">
+        <v>384</v>
+      </c>
+      <c r="B112" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="C112" s="13" t="s">
+        <v>385</v>
+      </c>
+      <c r="D112" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E112" s="13" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="B113" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="C113" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="D113" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E113" s="9" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" s="13" t="s">
+        <v>393</v>
+      </c>
+      <c r="B114" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="C114" s="13" t="s">
+        <v>394</v>
+      </c>
+      <c r="D114" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E114" s="13" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="B115" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="C115" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="D115" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E115" s="9" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" s="13" t="s">
+        <v>400</v>
+      </c>
+      <c r="B116" s="13" t="s">
+        <v>397</v>
+      </c>
+      <c r="C116" s="13" t="s">
+        <v>401</v>
+      </c>
+      <c r="D116" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="E116" s="13" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="B117" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="C117" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="D117" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E117" s="9" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" s="13" t="s">
+        <v>406</v>
+      </c>
+      <c r="B118" s="13" t="s">
+        <v>397</v>
+      </c>
+      <c r="C118" s="13" t="s">
+        <v>407</v>
+      </c>
+      <c r="D118" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="E118" s="13" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="B119" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="C119" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="D119" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E119" s="9" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" s="13" t="s">
+        <v>411</v>
+      </c>
+      <c r="B120" s="13" t="s">
+        <v>397</v>
+      </c>
+      <c r="C120" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="D120" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E120" s="13" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="B121" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="C121" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="D121" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E121" s="9" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" s="13" t="s">
+        <v>417</v>
+      </c>
+      <c r="B122" s="13" t="s">
+        <v>397</v>
+      </c>
+      <c r="C122" s="13" t="s">
+        <v>418</v>
+      </c>
+      <c r="D122" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E122" s="13" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="B123" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="C123" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="D123" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E123" s="9" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" s="13" t="s">
+        <v>423</v>
+      </c>
+      <c r="B124" s="13" t="s">
+        <v>397</v>
+      </c>
+      <c r="C124" s="13" t="s">
+        <v>424</v>
+      </c>
+      <c r="D124" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E124" s="13" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="B125" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="C125" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="D125" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E125" s="9" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" s="13" t="s">
+        <v>429</v>
+      </c>
+      <c r="B126" s="13" t="s">
+        <v>397</v>
+      </c>
+      <c r="C126" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="D126" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E126" s="13" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="B127" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="C127" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="D127" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E127" s="9" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="B128" s="13" t="s">
+        <v>433</v>
+      </c>
+      <c r="C128" s="13" t="s">
+        <v>437</v>
+      </c>
+      <c r="D128" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E128" s="13" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="B129" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="C129" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="D129" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E129" s="9" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" s="13" t="s">
+        <v>442</v>
+      </c>
+      <c r="B130" s="13" t="s">
+        <v>433</v>
+      </c>
+      <c r="C130" s="13" t="s">
+        <v>443</v>
+      </c>
+      <c r="D130" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E130" s="13" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="B131" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="C131" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="D131" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E131" s="9" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" s="13" t="s">
+        <v>451</v>
+      </c>
+      <c r="B132" s="13" t="s">
+        <v>433</v>
+      </c>
+      <c r="C132" s="13" t="s">
+        <v>452</v>
+      </c>
+      <c r="D132" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E132" s="13" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="B133" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="C133" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="D133" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E133" s="9" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" s="13" t="s">
+        <v>461</v>
+      </c>
+      <c r="B134" s="13" t="s">
+        <v>458</v>
+      </c>
+      <c r="C134" s="13" t="s">
+        <v>462</v>
+      </c>
+      <c r="D134" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="E134" s="13" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" s="9" t="s">
+        <v>479</v>
+      </c>
+      <c r="B135" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="C135" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="D135" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E135" s="9" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" s="13" t="s">
+        <v>482</v>
+      </c>
+      <c r="B136" s="13" t="s">
+        <v>458</v>
+      </c>
+      <c r="C136" s="13" t="s">
+        <v>483</v>
+      </c>
+      <c r="D136" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E136" s="13" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="B137" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="C137" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="D137" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E137" s="9" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" s="13" t="s">
+        <v>488</v>
+      </c>
+      <c r="B138" s="13" t="s">
+        <v>458</v>
+      </c>
+      <c r="C138" s="13" t="s">
+        <v>489</v>
+      </c>
+      <c r="D138" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E138" s="13" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="B139" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="C139" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="D139" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E139" s="9" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" s="13" t="s">
+        <v>541</v>
+      </c>
+      <c r="B140" s="13" t="s">
+        <v>526</v>
+      </c>
+      <c r="C140" s="13" t="s">
+        <v>542</v>
+      </c>
+      <c r="D140" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E140" s="13" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" s="9" t="s">
+        <v>544</v>
+      </c>
+      <c r="B141" s="9" t="s">
+        <v>545</v>
+      </c>
+      <c r="C141" s="9" t="s">
+        <v>546</v>
+      </c>
+      <c r="D141" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E141" s="9" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" s="13" t="s">
+        <v>551</v>
+      </c>
+      <c r="B142" s="13" t="s">
+        <v>545</v>
+      </c>
+      <c r="C142" s="13" t="s">
+        <v>552</v>
+      </c>
+      <c r="D142" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E142" s="13" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" s="9" t="s">
+        <v>561</v>
+      </c>
+      <c r="B143" s="9" t="s">
+        <v>562</v>
+      </c>
+      <c r="C143" s="9" t="s">
+        <v>563</v>
+      </c>
+      <c r="D143" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E143" s="9" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" s="13" t="s">
+        <v>574</v>
+      </c>
+      <c r="B144" s="13" t="s">
+        <v>562</v>
+      </c>
+      <c r="C144" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="D144" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E144" s="13" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" s="9" t="s">
+        <v>596</v>
+      </c>
+      <c r="B145" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="C145" s="9" t="s">
+        <v>597</v>
+      </c>
+      <c r="D145" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E145" s="9" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" s="13" t="s">
+        <v>599</v>
+      </c>
+      <c r="B146" s="13" t="s">
+        <v>578</v>
+      </c>
+      <c r="C146" s="13" t="s">
+        <v>546</v>
+      </c>
+      <c r="D146" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E146" s="13" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" s="9" t="s">
+        <v>601</v>
+      </c>
+      <c r="B147" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="C147" s="9" t="s">
+        <v>569</v>
+      </c>
+      <c r="D147" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E147" s="9" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" s="13" t="s">
+        <v>603</v>
+      </c>
+      <c r="B148" s="13" t="s">
+        <v>578</v>
+      </c>
+      <c r="C148" s="13" t="s">
+        <v>563</v>
+      </c>
+      <c r="D148" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E148" s="13" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" s="9" t="s">
+        <v>605</v>
+      </c>
+      <c r="B149" s="9" t="s">
+        <v>606</v>
+      </c>
+      <c r="C149" s="9" t="s">
+        <v>607</v>
+      </c>
+      <c r="D149" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E149" s="9" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="B150" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="C150" s="13" t="s">
+        <v>610</v>
+      </c>
+      <c r="D150" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="E150" s="13" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="B151" s="9" t="s">
+        <v>606</v>
+      </c>
+      <c r="C151" s="9" t="s">
+        <v>613</v>
+      </c>
+      <c r="D151" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E151" s="9" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" s="13" t="s">
+        <v>615</v>
+      </c>
+      <c r="B152" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="C152" s="13" t="s">
+        <v>616</v>
+      </c>
+      <c r="D152" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="E152" s="13" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" s="9" t="s">
+        <v>624</v>
+      </c>
+      <c r="B153" s="9" t="s">
+        <v>606</v>
+      </c>
+      <c r="C153" s="9" t="s">
+        <v>625</v>
+      </c>
+      <c r="D153" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E153" s="9" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" s="13" t="s">
+        <v>627</v>
+      </c>
+      <c r="B154" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="C154" s="13" t="s">
+        <v>628</v>
+      </c>
+      <c r="D154" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="E154" s="13" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" s="9" t="s">
+        <v>630</v>
+      </c>
+      <c r="B155" s="9" t="s">
+        <v>606</v>
+      </c>
+      <c r="C155" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="D155" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E155" s="9" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="B156" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="C156" s="13" t="s">
+        <v>530</v>
+      </c>
+      <c r="D156" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="E156" s="13" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="B157" s="9" t="s">
+        <v>606</v>
+      </c>
+      <c r="C157" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="D157" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E157" s="9" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A158" s="13" t="s">
+        <v>636</v>
+      </c>
+      <c r="B158" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="C158" s="13" t="s">
+        <v>536</v>
+      </c>
+      <c r="D158" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="E158" s="13" t="s">
+        <v>637</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
